--- a/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N41_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G3/G3_T1829_W0042F0003T0006Z000C1N41_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>71.86213102461197</v>
+        <v>11.67759629149945</v>
       </c>
       <c r="D2" t="n">
-        <v>35.81745766983526</v>
+        <v>5.82033687134823</v>
       </c>
       <c r="E2" t="n">
-        <v>10.7678531608143</v>
+        <v>1.749776138632324</v>
       </c>
       <c r="F2" t="n">
-        <v>13.04643470403224</v>
+        <v>2.12004563940524</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>53.78575908111144</v>
+        <v>8.740185850680609</v>
       </c>
       <c r="D3" t="n">
-        <v>32.90749810947616</v>
+        <v>5.347468442789876</v>
       </c>
       <c r="E3" t="n">
-        <v>10.7678531608143</v>
+        <v>1.749776138632324</v>
       </c>
       <c r="F3" t="n">
-        <v>13.04643470403224</v>
+        <v>2.12004563940524</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>55.49236364628879</v>
+        <v>9.01750909252193</v>
       </c>
       <c r="D4" t="n">
-        <v>27.35771270491092</v>
+        <v>4.445628314548025</v>
       </c>
       <c r="E4" t="n">
-        <v>10.7678531608143</v>
+        <v>1.749776138632324</v>
       </c>
       <c r="F4" t="n">
-        <v>13.04643470403224</v>
+        <v>2.12004563940524</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>79.34016731200727</v>
+        <v>12.89277718820118</v>
       </c>
       <c r="D5" t="n">
-        <v>39.17943054432744</v>
+        <v>6.366657463453209</v>
       </c>
       <c r="E5" t="n">
-        <v>10.7678531608143</v>
+        <v>1.749776138632324</v>
       </c>
       <c r="F5" t="n">
-        <v>13.04643470403224</v>
+        <v>2.12004563940524</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>55.89785170170197</v>
+        <v>9.083400901526572</v>
       </c>
       <c r="D6" t="n">
-        <v>53.93641475074819</v>
+        <v>8.764667396996581</v>
       </c>
       <c r="E6" t="n">
-        <v>10.7678531608143</v>
+        <v>1.749776138632324</v>
       </c>
       <c r="F6" t="n">
-        <v>13.04643470403224</v>
+        <v>2.12004563940524</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>77.08061511622361</v>
+        <v>12.52559995638634</v>
       </c>
       <c r="D7" t="n">
-        <v>65.16155137638896</v>
+        <v>10.58875209866321</v>
       </c>
       <c r="E7" t="n">
-        <v>10.7678531608143</v>
+        <v>1.749776138632324</v>
       </c>
       <c r="F7" t="n">
-        <v>13.04643470403224</v>
+        <v>2.12004563940524</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
